--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -755,7 +755,7 @@
         <v>0.8737864077669902</v>
       </c>
       <c r="C14" t="n">
-        <v>0.865979381443299</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="D14" t="n">
         <v>0.7946428571428571</v>
@@ -764,7 +764,7 @@
         <v>0.8712871287128713</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8514239437665044</v>
+        <v>0.8462693045912466</v>
       </c>
     </row>
     <row r="15">
@@ -777,7 +777,7 @@
         <v>0.6772727272727272</v>
       </c>
       <c r="C15" t="n">
-        <v>0.565018315018315</v>
+        <v>0.5206043956043956</v>
       </c>
       <c r="D15" t="n">
         <v>0.6010869565217392</v>
@@ -786,7 +786,7 @@
         <v>0.6025280898876404</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6114765221751055</v>
+        <v>0.6003730423216256</v>
       </c>
     </row>
     <row r="16">
@@ -799,7 +799,7 @@
         <v>0.7040883977900552</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5809238949817215</v>
+        <v>0.5164506480558325</v>
       </c>
       <c r="D16" t="n">
         <v>0.6105820105820106</v>
@@ -808,7 +808,7 @@
         <v>0.6223756111590452</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6294924786282081</v>
+        <v>0.6133741668967359</v>
       </c>
     </row>
     <row r="17">
@@ -821,7 +821,7 @@
         <v>0.8629083302043663</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8339106392163717</v>
+        <v>0.808358429865044</v>
       </c>
       <c r="D17" t="n">
         <v>0.7826908541194255</v>
@@ -830,7 +830,7 @@
         <v>0.8561095971547111</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8339048551737186</v>
+        <v>0.8275168028358867</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         <v>0.7613636363636365</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7358058608058609</v>
+        <v>0.6524725274725275</v>
       </c>
       <c r="D18" t="n">
         <v>0.6538043478260869</v>
@@ -852,7 +852,7 @@
         <v>0.7776217228464419</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7321488919605066</v>
+        <v>0.7113155586271733</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +868,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[82, 2], [11, 2]]</t>
+          <t>[[81, 3], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[84, 5], [11, 4]]</t>
+          <t>[[83, 5], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8514239437665044</v>
+        <v>0.8462693045912466</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03290356544704461</v>
+        <v>0.03181665406175824</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6114765221751055</v>
+        <v>0.6003730423216256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04085193732352397</v>
+        <v>0.05541153410656901</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6294924786282081</v>
+        <v>0.6133741668967359</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0456391117281178</v>
+        <v>0.06654333611783136</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8339048551737186</v>
+        <v>0.8275168028358867</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03145284592743611</v>
+        <v>0.03334110462197212</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7321488919605066</v>
+        <v>0.7113155586271733</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0476248901733301</v>
+        <v>0.05846229379236949</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[84, 5], [11, 4]]</t>
+          <t>[[83, 5], [11, 4]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7281553398058253</v>
+        <v>0.8155339805825242</v>
       </c>
       <c r="C8" t="n">
         <v>0.8144329896907216</v>
@@ -619,10 +619,10 @@
         <v>0.7767857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8118811881188119</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7828138079752682</v>
+        <v>0.8071337156941955</v>
       </c>
     </row>
     <row r="9">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7303030303030302</v>
+        <v>0.8090909090909091</v>
       </c>
       <c r="C9" t="n">
         <v>0.6002747252747254</v>
@@ -641,10 +641,10 @@
         <v>0.7663043478260869</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7490636704119851</v>
+        <v>0.7186329588014981</v>
       </c>
       <c r="F9" t="n">
-        <v>0.711486443453957</v>
+        <v>0.7235757352483049</v>
       </c>
     </row>
     <row r="10">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6302564102564102</v>
+        <v>0.7207875588529034</v>
       </c>
       <c r="C10" t="n">
         <v>0.6002747252747254</v>
@@ -663,10 +663,10 @@
         <v>0.6987627756858525</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6716852010265184</v>
+        <v>0.6658088235294117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6502447780608767</v>
+        <v>0.6714084708357233</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7650983320886233</v>
+        <v>0.8360623719572755</v>
       </c>
       <c r="C11" t="n">
         <v>0.8144329896907216</v>
@@ -685,10 +685,10 @@
         <v>0.7973180665488357</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8352471859675273</v>
+        <v>0.8398660454280722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.803024143573927</v>
+        <v>0.8219198684062262</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.8659090909090909</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8626373626373627</v>
+        <v>0.8562271062271063</v>
       </c>
       <c r="D12" t="n">
         <v>0.8315217391304348</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8127340823970036</v>
+        <v>0.7818352059925093</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8369505687684731</v>
+        <v>0.8338732855647852</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[64, 24], [4, 11]]</t>
+          <t>[[72, 16], [3, 12]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[74, 15], [4, 8]]</t>
+          <t>[[76, 13], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[71, 17], [6, 10]]</t>
+          <t>[[74, 14], [6, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7828138079752682</v>
+        <v>0.8071337156941955</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03488757406629255</v>
+        <v>0.01774417154212694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.711486443453957</v>
+        <v>0.7235757352483049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06545830891993905</v>
+        <v>0.07804830137431064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6502447780608767</v>
+        <v>0.6714084708357233</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03778302811256716</v>
+        <v>0.04549153254929453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.803024143573927</v>
+        <v>0.8219198684062262</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02568760753092594</v>
+        <v>0.01720012851639379</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8369505687684731</v>
+        <v>0.8338732855647852</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01796796928021497</v>
+        <v>0.032555635527758</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[71, 17], [6, 10]]</t>
+          <t>[[74, 14], [6, 10]]</t>
         </is>
       </c>
     </row>
